--- a/Excel/PetSpeicalAttrConfig.xlsx
+++ b/Excel/PetSpeicalAttrConfig.xlsx
@@ -128,13 +128,13 @@
     <t>攻击倍率</t>
   </si>
   <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>增伤倍率</t>
+  </si>
+  <si>
     <t>闪避</t>
-  </si>
-  <si>
-    <t>增伤倍率</t>
-  </si>
-  <si>
-    <t>命中</t>
   </si>
   <si>
     <t>破韧倍率</t>
@@ -1414,10 +1414,10 @@
         <v>1</v>
       </c>
       <c r="F16" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G16" s="1">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>22</v>
@@ -1454,10 +1454,10 @@
         <v>1</v>
       </c>
       <c r="F18" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G18" s="1">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>24</v>
@@ -1713,10 +1713,10 @@
         <v>2</v>
       </c>
       <c r="F33" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G33" s="1">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>22</v>
@@ -1753,10 +1753,10 @@
         <v>2</v>
       </c>
       <c r="F35" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G35" s="1">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>24</v>
@@ -1993,10 +1993,10 @@
         <v>3</v>
       </c>
       <c r="F49" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G49" s="1">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>22</v>
@@ -2033,10 +2033,10 @@
         <v>3</v>
       </c>
       <c r="F51" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G51" s="1">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>24</v>
